--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="2" min="2" max="2"/>
@@ -932,6 +932,86 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TbTerrain</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Terrain</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Terrain.xlsx</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Terrain</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TbLevelTerrain</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LevelTerrain</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LevelTerrain.xlsx</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LevelTerrain</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
